--- a/Improved_plan_Feasibility_and_KPI_results1.xlsx
+++ b/Improved_plan_Feasibility_and_KPI_results1.xlsx
@@ -614,7 +614,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3870.2004</v>
+        <v>4048.520400000001</v>
       </c>
     </row>
     <row r="3">
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3225167</v>
+        <v>3279167</v>
       </c>
     </row>
     <row r="4">
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3225.167</v>
+        <v>3279.167</v>
       </c>
     </row>
     <row r="5">
@@ -644,7 +644,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6">
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>33</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7">
@@ -664,7 +664,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>232</v>
+        <v>252.5</v>
       </c>
     </row>
     <row r="8">
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.866666666666667</v>
+        <v>4.208333333333333</v>
       </c>
     </row>
     <row r="9">
@@ -684,7 +684,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>11.6</v>
+        <v>18.03571428571428</v>
       </c>
     </row>
   </sheetData>
